--- a/public/demo-files/demo-board-products.xlsx
+++ b/public/demo-files/demo-board-products.xlsx
@@ -20,15 +20,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t xml:space="preserve">Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t xml:space="preserve">Product Code/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of Board (Raw Board)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Stock Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Stock At least</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bp0001</t>
   </si>
   <si>
     <t xml:space="preserve">HDF</t>
   </si>
   <si>
-    <t xml:space="preserve">MDF</t>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bp0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1 Particle Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCS</t>
   </si>
 </sst>
 </file>
@@ -38,11 +62,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -62,13 +87,28 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF202124"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,7 +153,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -122,8 +162,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -135,6 +183,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF202124"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -143,47 +251,89 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.06"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/public/demo-files/demo-board-products.xlsx
+++ b/public/demo-files/demo-board-products.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Product Code/ID</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">Unit</t>
   </si>
   <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
     <t xml:space="preserve">Low Stock Warning</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t xml:space="preserve">FT</t>
   </si>
   <si>
+    <t xml:space="preserve">18mm</t>
+  </si>
+  <si>
     <t xml:space="preserve">bp0002</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6mm</t>
   </si>
 </sst>
 </file>
@@ -153,7 +162,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -171,6 +180,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -251,13 +264,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -270,44 +283,53 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="0" t="n">
+      <c r="F2" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
+      <c r="A3" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="F3" s="0" t="n">
         <v>0</v>
       </c>
     </row>
